--- a/docs/testing/spreadsheet-output/sales-recap.xlsx
+++ b/docs/testing/spreadsheet-output/sales-recap.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="23">
   <si>
     <t>Tanggal</t>
   </si>
@@ -26,7 +26,7 @@
     <t>Total Omset (Rp)</t>
   </si>
   <si>
-    <t>31/12/2099</t>
+    <t>01/01/2099</t>
   </si>
   <si>
     <t>12/07/2026</t>
@@ -35,40 +35,55 @@
     <t>11/07/2026</t>
   </si>
   <si>
-    <t>08/07/2026</t>
-  </si>
-  <si>
-    <t>07/07/2026</t>
-  </si>
-  <si>
-    <t>05/07/2026</t>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>09/07/2026</t>
+  </si>
+  <si>
+    <t>04/07/2026</t>
   </si>
   <si>
     <t>03/07/2026</t>
   </si>
   <si>
+    <t>02/07/2026</t>
+  </si>
+  <si>
+    <t>01/07/2026</t>
+  </si>
+  <si>
     <t>30/06/2026</t>
   </si>
   <si>
+    <t>29/06/2026</t>
+  </si>
+  <si>
+    <t>28/06/2026</t>
+  </si>
+  <si>
     <t>26/06/2026</t>
   </si>
   <si>
+    <t>25/06/2026</t>
+  </si>
+  <si>
+    <t>24/06/2026</t>
+  </si>
+  <si>
     <t>22/06/2026</t>
   </si>
   <si>
     <t>21/06/2026</t>
   </si>
   <si>
-    <t>20/06/2026</t>
-  </si>
-  <si>
-    <t>19/06/2026</t>
-  </si>
-  <si>
     <t>17/06/2026</t>
   </si>
   <si>
-    <t>16/06/2026</t>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>14/06/2026</t>
   </si>
 </sst>
 </file>
@@ -408,7 +423,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
@@ -443,10 +458,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>1024000.0</v>
+        <v>1873000.0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -454,10 +469,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>1249000.0</v>
+        <v>2334000.0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -465,10 +480,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1687000.0</v>
+        <v>76000.0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -479,7 +494,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>452000.0</v>
+        <v>51000.0</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -490,7 +505,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>561000.0</v>
+        <v>46000.0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -501,7 +516,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>856000.0</v>
+        <v>617000.0</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -512,7 +527,7 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>1448000.0</v>
+        <v>1708000.0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -523,7 +538,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>675000.0</v>
+        <v>655000.0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -534,7 +549,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>245000.0</v>
+        <v>1750000.0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -545,7 +560,7 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>1754000.0</v>
+        <v>525000.0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -553,10 +568,10 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>1081000.0</v>
+        <v>594000.0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -567,7 +582,7 @@
         <v>2</v>
       </c>
       <c r="C14">
-        <v>1548000.0</v>
+        <v>828000.0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -578,7 +593,7 @@
         <v>1</v>
       </c>
       <c r="C15">
-        <v>1111000.0</v>
+        <v>51000.0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -586,10 +601,65 @@
         <v>17</v>
       </c>
       <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>446000.0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1288000.0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>278000.0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>810000.0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20">
         <v>2</v>
       </c>
-      <c r="C16">
-        <v>3003000.0</v>
+      <c r="C20">
+        <v>964000.0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>324000.0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/testing/spreadsheet-output/sales-recap.xlsx
+++ b/docs/testing/spreadsheet-output/sales-recap.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
   <si>
     <t>Tanggal</t>
   </si>
@@ -26,10 +26,19 @@
     <t>Total Omset (Rp)</t>
   </si>
   <si>
-    <t>01/01/2099</t>
-  </si>
-  <si>
-    <t>12/07/2026</t>
+    <t>17/07/2026</t>
+  </si>
+  <si>
+    <t>16/07/2026</t>
+  </si>
+  <si>
+    <t>15/07/2026</t>
+  </si>
+  <si>
+    <t>14/07/2026</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
   </si>
   <si>
     <t>11/07/2026</t>
@@ -41,7 +50,10 @@
     <t>09/07/2026</t>
   </si>
   <si>
-    <t>04/07/2026</t>
+    <t>08/07/2026</t>
+  </si>
+  <si>
+    <t>07/07/2026</t>
   </si>
   <si>
     <t>03/07/2026</t>
@@ -50,19 +62,7 @@
     <t>02/07/2026</t>
   </si>
   <si>
-    <t>01/07/2026</t>
-  </si>
-  <si>
-    <t>30/06/2026</t>
-  </si>
-  <si>
-    <t>29/06/2026</t>
-  </si>
-  <si>
-    <t>28/06/2026</t>
-  </si>
-  <si>
-    <t>26/06/2026</t>
+    <t>27/06/2026</t>
   </si>
   <si>
     <t>25/06/2026</t>
@@ -71,19 +71,10 @@
     <t>24/06/2026</t>
   </si>
   <si>
-    <t>22/06/2026</t>
-  </si>
-  <si>
-    <t>21/06/2026</t>
-  </si>
-  <si>
-    <t>17/06/2026</t>
-  </si>
-  <si>
-    <t>15/06/2026</t>
-  </si>
-  <si>
-    <t>14/06/2026</t>
+    <t>23/06/2026</t>
+  </si>
+  <si>
+    <t>18/06/2026</t>
   </si>
 </sst>
 </file>
@@ -423,7 +414,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
@@ -447,10 +438,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>1500000.0</v>
+        <v>346000.0</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -458,10 +449,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
-        <v>1873000.0</v>
+        <v>909000.0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -469,10 +460,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>2334000.0</v>
+        <v>232000.0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -483,7 +474,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>76000.0</v>
+        <v>531000.0</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -491,10 +482,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6">
-        <v>51000.0</v>
+        <v>2229000.0</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -505,7 +496,7 @@
         <v>1</v>
       </c>
       <c r="C7">
-        <v>46000.0</v>
+        <v>92000.0</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -516,7 +507,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>617000.0</v>
+        <v>1736000.0</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -527,7 +518,7 @@
         <v>1</v>
       </c>
       <c r="C9">
-        <v>1708000.0</v>
+        <v>921000.0</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -538,7 +529,7 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>655000.0</v>
+        <v>887000.0</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -546,10 +537,10 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11">
-        <v>1750000.0</v>
+        <v>2230000.0</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -560,7 +551,7 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>525000.0</v>
+        <v>979000.0</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -568,10 +559,10 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13">
-        <v>594000.0</v>
+        <v>939000.0</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -579,10 +570,10 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14">
-        <v>828000.0</v>
+        <v>551000.0</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -593,7 +584,7 @@
         <v>1</v>
       </c>
       <c r="C15">
-        <v>51000.0</v>
+        <v>1580000.0</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -601,10 +592,10 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <v>446000.0</v>
+        <v>1255000.0</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -615,7 +606,7 @@
         <v>1</v>
       </c>
       <c r="C17">
-        <v>1288000.0</v>
+        <v>1692000.0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -626,40 +617,7 @@
         <v>1</v>
       </c>
       <c r="C18">
-        <v>278000.0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>810000.0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20">
-        <v>964000.0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>324000.0</v>
+        <v>2553000.0</v>
       </c>
     </row>
   </sheetData>
